--- a/docs/zoho-books-apis-webhooks-module-wise.xlsx
+++ b/docs/zoho-books-apis-webhooks-module-wise.xlsx
@@ -487,9 +487,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -704,7 +702,7 @@
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
         <v>1</v>
@@ -752,7 +750,7 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -774,9 +772,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
@@ -816,7 +812,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Stock webhook is custom — not a native Zoho Books webhook; requires middleware or custom Zoho function.</t>
+          <t>Stock and shipment webhooks are custom inbound endpoints; shipment webhook is deployed on UAT and persists zoho_shipment_webhook_event.</t>
         </is>
       </c>
     </row>
@@ -843,7 +839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H67"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2527,7 +2523,7 @@
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>Order tracking — detect HAND_WRAPPED / package created</t>
+          <t>Scheduler/admin fallback for order tracking; shipment webhook is primary event path</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr">
@@ -2831,170 +2827,170 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>Our Admin APIs</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>Our Admin API</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>/api/v1/admin/zoho/oauth-setup</t>
-        </is>
-      </c>
-      <c r="E48" s="5" t="inlineStr">
-        <is>
-          <t>Our backend</t>
-        </is>
-      </c>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>OAuth setup hints for Zoho API Console</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="inlineStr">
-        <is>
-          <t>Admin Zoho settings page</t>
-        </is>
-      </c>
-      <c r="H48" s="5" t="inlineStr">
-        <is>
-          <t>ZohoAdminResource</t>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Inbound Webhooks</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Inbound Webhook (Our endpoint)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>/api/v1/zoho/shipment-webhook</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>https://uat.minisnmore.com (public)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Receive package/shipment tracking events from Zoho; update store order tracking/status</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Zoho Inventory workflow pushes Package Created, Shipment Updated, Shipment Delivered</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>InternalZohoShipmentWebhookResource -&gt; ZohoShipmentWebhookHandlerService</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>Our Admin APIs</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>Our Admin API</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>/api/v1/admin/zoho/integration-status</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>Our backend</t>
-        </is>
-      </c>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t>Local integration status + last pull cursor</t>
-        </is>
-      </c>
-      <c r="G49" s="5" t="inlineStr">
-        <is>
-          <t>Admin dashboard</t>
-        </is>
-      </c>
-      <c r="H49" s="5" t="inlineStr">
-        <is>
-          <t>ZohoAdminResource</t>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Inbound Webhooks</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Inbound Webhook (Internal path)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>/internal/v1/zoho/shipment-webhook</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Backend internal route</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Same shipment webhook (internal routing)</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Nginx / gateway proxy to backend</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>InternalZohoShipmentWebhookResource</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>Our Admin APIs</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>Our Admin API</t>
-        </is>
-      </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
-        <is>
-          <t>/api/v1/admin/zoho/connect-url</t>
-        </is>
-      </c>
-      <c r="E50" s="5" t="inlineStr">
-        <is>
-          <t>Our backend</t>
-        </is>
-      </c>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>Build Zoho OAuth authorize URL</t>
-        </is>
-      </c>
-      <c r="G50" s="5" t="inlineStr">
-        <is>
-          <t>Admin Connect to Zoho button</t>
-        </is>
-      </c>
-      <c r="H50" s="5" t="inlineStr">
-        <is>
-          <t>ZohoAdminResource → ZohoOAuthService</t>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Inbound Webhooks</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Webhook Auth Header</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>X-Zoho-Shipment-Signature or X-Zoho-Shipment-Secret</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>HMAC-SHA256 signature or shared secret for raw JSON body</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Must match application.zoho.shipment-webhook-secret</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>WebhookHmacSupport / ApplicationProperties.Zoho</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>Our Admin APIs</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>Our Admin API</t>
-        </is>
-      </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="inlineStr">
-        <is>
-          <t>/api/v1/admin/zoho/oauth/complete</t>
-        </is>
-      </c>
-      <c r="E51" s="5" t="inlineStr">
-        <is>
-          <t>Our backend</t>
-        </is>
-      </c>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>Complete OAuth; stores refresh token</t>
-        </is>
-      </c>
-      <c r="G51" s="5" t="inlineStr">
-        <is>
-          <t>OAuth redirect callback</t>
-        </is>
-      </c>
-      <c r="H51" s="5" t="inlineStr">
-        <is>
-          <t>ZohoAdminResource → ZohoOAuthService</t>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Inbound Webhooks</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Webhook Payload Fields</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>eventId, zohoSalesOrderId, salesorder_number, package_id?, shipment_id?, status, tracking_number?, carrier?, shipment_date?</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Idempotent tracking update; duplicate eventId ignored</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Persists zoho_shipment_webhook_event</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>ZohoShipmentWebhookHandlerService</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3012,7 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>/api/v1/admin/zoho/test</t>
+          <t>/api/v1/admin/zoho/oauth-setup</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -3026,17 +3022,17 @@
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>Test Zoho connection (calls GET /organizations)</t>
+          <t>OAuth setup hints for Zoho API Console</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>Admin Test Connection</t>
+          <t>Admin Zoho settings page</t>
         </is>
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
-          <t>ZohoAdminResource → ZohoSyncService.testConnection</t>
+          <t>ZohoAdminResource</t>
         </is>
       </c>
     </row>
@@ -3053,12 +3049,12 @@
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>/api/v1/admin/zoho/pull-products-auto-create-category</t>
+          <t>/api/v1/admin/zoho/integration-status</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -3068,12 +3064,12 @@
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>Toggle auto-create categories on pull</t>
+          <t>Local integration status + last pull cursor</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Admin setting</t>
+          <t>Admin dashboard</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -3095,12 +3091,12 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>/api/v1/admin/zoho/sync-products</t>
+          <t>/api/v1/admin/zoho/connect-url</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -3110,17 +3106,17 @@
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>Bulk push all products to Zoho</t>
+          <t>Build Zoho OAuth authorize URL</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>Admin Sync to Zoho</t>
+          <t>Admin Connect to Zoho button</t>
         </is>
       </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
-          <t>ZohoAdminResource → ZohoSyncService.syncAllProducts</t>
+          <t>ZohoAdminResource → ZohoOAuthService</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3138,7 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>/api/v1/admin/zoho/sync-products/{id}</t>
+          <t>/api/v1/admin/zoho/oauth/complete</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -3152,17 +3148,17 @@
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>Push single product to Zoho</t>
+          <t>Complete OAuth; stores refresh token</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>Save product / manual sync</t>
+          <t>OAuth redirect callback</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>ZohoAdminResource → ZohoSyncService.syncProduct</t>
+          <t>ZohoAdminResource → ZohoOAuthService</t>
         </is>
       </c>
     </row>
@@ -3179,12 +3175,12 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>/api/v1/admin/zoho/sync-stock/{id}</t>
+          <t>/api/v1/admin/zoho/test</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -3194,17 +3190,17 @@
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>Push stock only for one product</t>
+          <t>Test Zoho connection (calls GET /organizations)</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>Admin stock sync</t>
+          <t>Admin Test Connection</t>
         </is>
       </c>
       <c r="H56" s="5" t="inlineStr">
         <is>
-          <t>ZohoAdminResource → ZohoSyncService.syncProductStockOnly</t>
+          <t>ZohoAdminResource → ZohoSyncService.testConnection</t>
         </is>
       </c>
     </row>
@@ -3221,12 +3217,12 @@
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>/api/v1/admin/zoho/pull-products</t>
+          <t>/api/v1/admin/zoho/pull-products-auto-create-category</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -3236,17 +3232,17 @@
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>Incremental pull products from Zoho</t>
+          <t>Toggle auto-create categories on pull</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>Admin Pull Products (default)</t>
+          <t>Admin setting</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>ZohoAdminResource → ZohoSyncService.pullProducts</t>
+          <t>ZohoAdminResource</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3264,7 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>/api/v1/admin/zoho/pull-products?full=true</t>
+          <t>/api/v1/admin/zoho/sync-products</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -3278,17 +3274,17 @@
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>Full catalog pull from Zoho</t>
+          <t>Bulk push all products to Zoho</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>Admin full rebuild (API only)</t>
+          <t>Admin Sync to Zoho</t>
         </is>
       </c>
       <c r="H58" s="5" t="inlineStr">
         <is>
-          <t>ZohoAdminResource → ZohoSyncService.pullProducts(full=true)</t>
+          <t>ZohoAdminResource → ZohoSyncService.syncAllProducts</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3306,7 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>/api/v1/admin/zoho/pull-products/{id}</t>
+          <t>/api/v1/admin/zoho/sync-products/{id}</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -3320,17 +3316,17 @@
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>Pull single product by store ID</t>
+          <t>Push single product to Zoho</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>Admin per-product pull</t>
+          <t>Save product / manual sync</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>ZohoAdminResource → ZohoSyncService.pullProduct</t>
+          <t>ZohoAdminResource → ZohoSyncService.syncProduct</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3348,7 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>/api/v1/admin/zoho/pull-products/{id}/variants</t>
+          <t>/api/v1/admin/zoho/sync-stock/{id}</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -3362,17 +3358,17 @@
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>Pull one variant row (sku, zohoItemId)</t>
+          <t>Push stock only for one product</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>Variant matrix pull</t>
+          <t>Admin stock sync</t>
         </is>
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>ZohoAdminResource → ZohoSyncService.pullProductVariant</t>
+          <t>ZohoAdminResource → ZohoSyncService.syncProductStockOnly</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3390,7 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>/api/v1/admin/zoho/pull-product</t>
+          <t>/api/v1/admin/zoho/pull-products</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -3404,17 +3400,17 @@
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>Pull external product by SKU / Zoho item ID</t>
+          <t>Incremental pull products from Zoho</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Import unknown Zoho item</t>
+          <t>Admin Pull Products (default)</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>ZohoAdminResource → ZohoSyncService.pullExternalProduct</t>
+          <t>ZohoAdminResource → ZohoSyncService.pullProducts</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3432,7 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>/api/v1/admin/zoho/pull-inventory</t>
+          <t>/api/v1/admin/zoho/pull-products?full=true</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -3446,17 +3442,17 @@
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>Pull stock only from Zoho</t>
+          <t>Full catalog pull from Zoho</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>Admin Pull Inventory + scheduler</t>
+          <t>Admin full rebuild (API only)</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
         <is>
-          <t>ZohoAdminResource → ZohoSyncService.pullInventory</t>
+          <t>ZohoAdminResource → ZohoSyncService.pullProducts(full=true)</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3474,7 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>/api/v1/admin/zoho/retry-orders</t>
+          <t>/api/v1/admin/zoho/pull-products/{id}</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -3488,17 +3484,17 @@
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>Retry failed Zoho order syncs</t>
+          <t>Pull single product by store ID</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>Admin / ZohoSyncScheduler</t>
+          <t>Admin per-product pull</t>
         </is>
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>ZohoAdminResource → ZohoSyncService.retryFailedOrders</t>
+          <t>ZohoAdminResource → ZohoSyncService.pullProduct</t>
         </is>
       </c>
     </row>
@@ -3520,7 +3516,7 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>/api/v1/admin/zoho/sync-orders/by-number/{orderNumber}</t>
+          <t>/api/v1/admin/zoho/pull-products/{id}/variants</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -3530,17 +3526,17 @@
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>Sync one order to Zoho by order number</t>
+          <t>Pull one variant row (sku, zohoItemId)</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>Admin manual order sync</t>
+          <t>Variant matrix pull</t>
         </is>
       </c>
       <c r="H64" s="5" t="inlineStr">
         <is>
-          <t>ZohoAdminResource → ZohoSyncService.syncOrder</t>
+          <t>ZohoAdminResource → ZohoSyncService.pullProductVariant</t>
         </is>
       </c>
     </row>
@@ -3562,7 +3558,7 @@
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>/api/v1/admin/zoho/pull-order-tracking</t>
+          <t>/api/v1/admin/zoho/pull-product</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -3572,17 +3568,17 @@
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>Pull tracking for all eligible orders</t>
+          <t>Pull external product by SKU / Zoho item ID</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>Admin + scheduled job (~15 min)</t>
+          <t>Import unknown Zoho item</t>
         </is>
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>ZohoAdminResource → ZohoSyncService.pullAllTracking</t>
+          <t>ZohoAdminResource → ZohoSyncService.pullExternalProduct</t>
         </is>
       </c>
     </row>
@@ -3599,12 +3595,12 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>/api/v1/admin/zoho-settings</t>
+          <t>/api/v1/admin/zoho/pull-inventory</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -3614,17 +3610,17 @@
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>Read Zoho settings (non-secret fields)</t>
+          <t>Pull stock only from Zoho</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>Admin settings</t>
+          <t>Admin Pull Inventory + scheduler</t>
         </is>
       </c>
       <c r="H66" s="5" t="inlineStr">
         <is>
-          <t>ZohoSettingsResource</t>
+          <t>ZohoAdminResource → ZohoSyncService.pullInventory</t>
         </is>
       </c>
     </row>
@@ -3641,30 +3637,198 @@
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/admin/zoho/retry-orders</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>Our backend</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>Retry failed Zoho order syncs</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>Admin / ZohoSyncScheduler</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>ZohoAdminResource → ZohoSyncService.retryFailedOrders</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>Our Admin APIs</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>Our Admin API</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/admin/zoho/sync-orders/by-number/{orderNumber}</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>Our backend</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>Sync one order to Zoho by order number</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>Admin manual order sync</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="inlineStr">
+        <is>
+          <t>ZohoAdminResource → ZohoSyncService.syncOrder</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>Our Admin APIs</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>Our Admin API</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/admin/zoho/pull-order-tracking</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>Our backend</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>Pull tracking for all eligible orders</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>Admin + scheduled job (~15 min)</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>ZohoAdminResource → ZohoSyncService.pullAllTracking</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>Our Admin APIs</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>Our Admin API</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/admin/zoho-settings</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>Our backend</t>
+        </is>
+      </c>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>Read Zoho settings (non-secret fields)</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>Admin settings</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="inlineStr">
+        <is>
+          <t>ZohoSettingsResource</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>Our Admin APIs</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>Our Admin API</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
           <t>PUT</t>
         </is>
       </c>
-      <c r="D67" s="5" t="inlineStr">
+      <c r="D71" s="5" t="inlineStr">
         <is>
           <t>/api/v1/admin/zoho-settings</t>
         </is>
       </c>
-      <c r="E67" s="5" t="inlineStr">
+      <c r="E71" s="5" t="inlineStr">
         <is>
           <t>Our backend</t>
         </is>
       </c>
-      <c r="F67" s="5" t="inlineStr">
+      <c r="F71" s="5" t="inlineStr">
         <is>
           <t>Save Zoho org ID, client ID, tokens</t>
         </is>
       </c>
-      <c r="G67" s="5" t="inlineStr">
+      <c r="G71" s="5" t="inlineStr">
         <is>
           <t>Admin settings</t>
         </is>
       </c>
-      <c r="H67" s="5" t="inlineStr">
+      <c r="H71" s="5" t="inlineStr">
         <is>
           <t>ZohoSettingsResource</t>
         </is>
@@ -3757,7 +3921,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/docs/zoho-books-apis-webhooks-module-wise.xlsx
+++ b/docs/zoho-books-apis-webhooks-module-wise.xlsx
@@ -622,7 +622,7 @@
         <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
         <v>5</v>
@@ -670,7 +670,7 @@
         <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>2</v>
@@ -750,7 +750,7 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -812,7 +812,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Stock and shipment webhooks are custom inbound endpoints; shipment webhook is deployed on UAT and persists zoho_shipment_webhook_event.</t>
+          <t>Stock, shipment, item/catalog, and order-status webhooks are custom inbound endpoints. Item and order-status webhooks are deployed on UAT, persist zoho_item_webhook_event / zoho_order_status_webhook_event, and use HMAC or shared-secret auth headers.</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H71"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3831,6 +3831,342 @@
       <c r="H71" s="5" t="inlineStr">
         <is>
           <t>ZohoSettingsResource</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>Inbound Webhooks</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>Inbound Webhook (Our endpoint)</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/zoho/item-webhook</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>https://uat.minisnmore.com (public)</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>Receive Zoho item created/edited/inactive events; run single item pull/merge</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>Zoho Items workflow pushes item changes; replaces full-list polling for changed catalog rows</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
+          <t>InternalZohoItemWebhookResource -&gt; ZohoItemWebhookHandlerService</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>Inbound Webhooks</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>Inbound Webhook (Internal path)</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>/internal/v1/zoho/item-webhook</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>Backend internal route</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>Same item webhook (internal routing)</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>Gateway proxy to catalog core</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>InternalZohoItemWebhookResource</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>Inbound Webhooks</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>Webhook Auth Header</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>X-Zoho-Item-Signature or X-Zoho-Item-Secret</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>HMAC-SHA256 signature or shared secret for raw JSON body</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>Must match application.zoho.item-webhook-secret</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="inlineStr">
+        <is>
+          <t>WebhookHmacSupport / ApplicationProperties.Zoho</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>Inbound Webhooks</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>Webhook Payload Fields</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>eventId, item_id|zohoItemId?, sku?, status?, last_modified_time?</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>Idempotent single-item catalog merge; duplicate eventId ignored</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>Persists zoho_item_webhook_event; failed pull releases idempotency claim</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>ZohoItemWebhookHandlerService -&gt; ZohoSyncService.pullExternalProduct</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>Inbound Webhooks</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>Inbound Webhook (Our endpoint)</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/zoho/order-status-webhook</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>https://uat.minisnmore.com (public)</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="inlineStr">
+        <is>
+          <t>Receive Zoho sales-order status/void events; update store order status/tracking</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>Zoho Sales Order workflow pushes void/status changes</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="inlineStr">
+        <is>
+          <t>InternalZohoOrderStatusWebhookResource -&gt; ZohoOrderStatusWebhookHandlerService</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>Inbound Webhooks</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>Inbound Webhook (Internal path)</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>/internal/v1/zoho/order-status-webhook</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>Backend internal route</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>Same order-status webhook (internal routing)</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>Gateway proxy to catalog core</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>InternalZohoOrderStatusWebhookResource</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>Inbound Webhooks</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>Webhook Auth Header</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>X-Zoho-Order-Status-Signature or X-Zoho-Order-Status-Secret</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>HMAC-SHA256 signature or shared secret for raw JSON body</t>
+        </is>
+      </c>
+      <c r="G78" s="5" t="inlineStr">
+        <is>
+          <t>Must match application.zoho.order-status-webhook-secret</t>
+        </is>
+      </c>
+      <c r="H78" s="5" t="inlineStr">
+        <is>
+          <t>WebhookHmacSupport / ApplicationProperties.Zoho</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>Inbound Webhooks</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>Webhook Payload Fields</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>eventId, zohoSalesOrderId|salesorder_id, salesorder_number?, status, tracking fields?</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>Idempotent status update; duplicate eventId ignored</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>Persists zoho_order_status_webhook_event; void -&gt; CANCELLED</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>ZohoOrderStatusWebhookHandlerService -&gt; ZohoOrderStatus.applySalesOrderTracking</t>
         </is>
       </c>
     </row>
@@ -3921,7 +4257,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
